--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XI-XX/FRACC XVI/LTAIPT_A63F16A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XI-XX/FRACC XVI/LTAIPT_A63F16A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -142,94 +142,94 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Contrato</t>
+  </si>
+  <si>
+    <t>Contrato Colectivo de Trabajo del Sindicato de Trabajadores Académicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>01/02/2020</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202020/Subdireccion%20Juridica/3er_Trimestre/Contrato_Coletivo_de_Trabajo.pdf</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Condiciones</t>
+  </si>
+  <si>
+    <t>Condiciones Generales de Trabajo del Sindicato de Trabajadores Administrativos y de Intendencia del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
     <t>Confianza</t>
   </si>
   <si>
+    <t>Ley Federal</t>
+  </si>
+  <si>
+    <t>Ley Federal del Trabajo</t>
+  </si>
+  <si>
+    <t>05/04/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/LEY%20FEDERAL%20DEL%20TRAB.22.pdf</t>
+  </si>
+  <si>
     <t>Ley Local</t>
   </si>
   <si>
     <t>Ley Laboral de los Servidores Públicos del Estado de Tlaxcala y sus Municipios</t>
   </si>
   <si>
+    <t>22/12/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/Ley_laboral_de_SERVIDORES%20PUB21.pdf</t>
+  </si>
+  <si>
+    <t>B6D1B292D789C77CDB5251BDB7D6146C</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>28/08/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Sub%20Juridica/</t>
+  </si>
+  <si>
+    <t>12/10/2023</t>
+  </si>
+  <si>
+    <t>C5807889FA2C4B3F0A1EC3DCD45C87E0</t>
+  </si>
+  <si>
+    <t>01/05/1970</t>
+  </si>
+  <si>
+    <t>D9F50BF59AF7C4B65EC3E908ADDD3198</t>
+  </si>
+  <si>
     <t>31/12/2007</t>
   </si>
   <si>
-    <t>22/12/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/Ley_laboral_de_SERVIDORES%20PUB21.pdf</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Ley Federal</t>
-  </si>
-  <si>
-    <t>Ley Federal del Trabajo</t>
-  </si>
-  <si>
-    <t>01/05/1970</t>
-  </si>
-  <si>
-    <t>05/04/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/LEY%20FEDERAL%20DEL%20TRAB.22.pdf</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Condiciones</t>
-  </si>
-  <si>
-    <t>Condiciones Generales de Trabajo del Sindicato de Trabajadores Administrativos y de Intendencia del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>22/03/2019</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/condiciones%20generales%20de%20trabajo/</t>
-  </si>
-  <si>
-    <t>Contrato</t>
-  </si>
-  <si>
-    <t>01/02/2020</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202020/Subdireccion%20Juridica/3er_Trimestre/Contrato_Coletivo_de_Trabajo.pdf</t>
-  </si>
-  <si>
-    <t>E41BFC0F52ACE57D4C3D840D4B86960E</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>3ECB36D657D9C1D8B277709B68D9FBC2</t>
-  </si>
-  <si>
-    <t>1B808F24AAEC5F64BE705B4037DD0AC6</t>
-  </si>
-  <si>
-    <t>8940E54CB57FAC1A75B2D7EC66F14717</t>
-  </si>
-  <si>
-    <t>Contrato Colectivo de Trabajo del Sindicato de Trabajdadores Académicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
+    <t>C496B775E2537ABB5F0916146FEBBB6E</t>
   </si>
   <si>
     <t>Otro</t>
@@ -703,7 +703,7 @@
   <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -712,7 +712,7 @@
     <col min="7" max="7" width="124.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="128.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="172.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
@@ -899,90 +899,90 @@
     </row>
     <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -993,13 +993,13 @@
         <v>40</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>55</v>
@@ -1008,7 +1008,7 @@
         <v>56</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>57</v>
@@ -1017,60 +1017,60 @@
         <v>58</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K11" s="2" t="s">
+      <c r="M11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1084,10 +1084,10 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E188">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E197">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F188">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F197">
       <formula1>Hidden_25</formula1>
     </dataValidation>
   </dataValidations>
@@ -1102,12 +1102,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -1152,7 +1152,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -1162,7 +1162,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -1207,7 +1207,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
